--- a/Fitness journey - youtube channels for fundementals .xlsx
+++ b/Fitness journey - youtube channels for fundementals .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolashovsepyan/Library/CloudStorage/Dropbox/PERSONAL/COWORK/Fitness Journey - 2.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0639189B-6012-B942-B967-B7967BBF4EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D9B06E-4D86-B04B-B463-B72703CB90AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13320" yWindow="600" windowWidth="27640" windowHeight="16680" xr2:uid="{3B813B38-9D01-754C-A2A0-8F51200B5372}"/>
+    <workbookView xWindow="640" yWindow="600" windowWidth="27640" windowHeight="16680" xr2:uid="{3B813B38-9D01-754C-A2A0-8F51200B5372}"/>
   </bookViews>
   <sheets>
     <sheet name="youtube library " sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="94">
   <si>
     <t>all 10 of these should be on our eseesntial list</t>
   </si>
@@ -318,6 +318,9 @@
   </si>
   <si>
     <t xml:space="preserve">breakdanse flare move </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=2vcgPfcK9FA&amp;t=21s </t>
   </si>
 </sst>
 </file>
@@ -685,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E93B59B1-3800-3645-A100-26B6C7D51E0C}">
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.33203125" style="2" customWidth="1"/>
@@ -1066,6 +1069,11 @@
       </c>
       <c r="B95" s="1" t="s">
         <v>91</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1111,6 +1119,7 @@
     <hyperlink ref="B88" r:id="rId39" xr:uid="{8B5086B5-57D9-1C4D-AE28-DCB6AF298BC3}"/>
     <hyperlink ref="B89" r:id="rId40" xr:uid="{E8F64A40-F736-F74B-A8FD-A0269635123F}"/>
     <hyperlink ref="B95" r:id="rId41" xr:uid="{2BCCB383-70B6-1F44-81C3-69650BC37711}"/>
+    <hyperlink ref="B97" r:id="rId42" xr:uid="{5ED3FC1A-5D85-F64E-8C6E-B8CFCD5F9DDE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
